--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/126.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/126.xlsx
@@ -426,13 +426,13 @@
         <v>-19.36755104332377</v>
       </c>
       <c r="E2">
-        <v>-9.006000230988018</v>
+        <v>-13.14638401620103</v>
       </c>
       <c r="F2">
-        <v>-4.569822291942831</v>
+        <v>-5.264037250593763</v>
       </c>
       <c r="G2">
-        <v>-9.164696925581095</v>
+        <v>-10.33879845381132</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-19.25273585019482</v>
       </c>
       <c r="E3">
-        <v>-8.988995811089216</v>
+        <v>-13.03724326414216</v>
       </c>
       <c r="F3">
-        <v>-4.050206472616965</v>
+        <v>-5.755445503119499</v>
       </c>
       <c r="G3">
-        <v>-9.100637869396198</v>
+        <v>-10.30066427974445</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-19.03367101971823</v>
       </c>
       <c r="E4">
-        <v>-9.905789902416087</v>
+        <v>-13.86366712817196</v>
       </c>
       <c r="F4">
-        <v>-4.268555007953484</v>
+        <v>-5.535360709706713</v>
       </c>
       <c r="G4">
-        <v>-8.508450793876909</v>
+        <v>-10.20586680822742</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-18.70243459722764</v>
       </c>
       <c r="E5">
-        <v>-10.83890914254061</v>
+        <v>-14.26643866336218</v>
       </c>
       <c r="F5">
-        <v>-4.221888101949371</v>
+        <v>-5.142969697939809</v>
       </c>
       <c r="G5">
-        <v>-8.798335403477651</v>
+        <v>-10.13681875991484</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-18.26737675634181</v>
       </c>
       <c r="E6">
-        <v>-11.50246643888455</v>
+        <v>-14.59330391723583</v>
       </c>
       <c r="F6">
-        <v>-4.595246544269553</v>
+        <v>-5.302379892567143</v>
       </c>
       <c r="G6">
-        <v>-8.326754812499548</v>
+        <v>-9.427958127955019</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-17.74788922722032</v>
       </c>
       <c r="E7">
-        <v>-12.11775925925473</v>
+        <v>-15.7996848644052</v>
       </c>
       <c r="F7">
-        <v>-4.199672944941095</v>
+        <v>-5.084120820910127</v>
       </c>
       <c r="G7">
-        <v>-8.429385034762495</v>
+        <v>-9.822522187507516</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-17.13511509028946</v>
       </c>
       <c r="E8">
-        <v>-11.07245613253819</v>
+        <v>-16.81620048185498</v>
       </c>
       <c r="F8">
-        <v>-4.023371510603276</v>
+        <v>-5.266771691390404</v>
       </c>
       <c r="G8">
-        <v>-8.076633165370993</v>
+        <v>-9.305974456469494</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-16.44351318268378</v>
       </c>
       <c r="E9">
-        <v>-12.54945415793194</v>
+        <v>-16.95715376381773</v>
       </c>
       <c r="F9">
-        <v>-4.216135090336929</v>
+        <v>-4.98372352005823</v>
       </c>
       <c r="G9">
-        <v>-7.778498676286386</v>
+        <v>-9.359204718195436</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-15.67497684271132</v>
       </c>
       <c r="E10">
-        <v>-14.58533380298233</v>
+        <v>-17.88583509941474</v>
       </c>
       <c r="F10">
-        <v>-4.03108692459295</v>
+        <v>-5.165474783539066</v>
       </c>
       <c r="G10">
-        <v>-7.149253354000494</v>
+        <v>-8.9846164904269</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-14.83520027044458</v>
       </c>
       <c r="E11">
-        <v>-15.73176228276416</v>
+        <v>-18.7756440141299</v>
       </c>
       <c r="F11">
-        <v>-4.141443686728706</v>
+        <v>-4.653716029028754</v>
       </c>
       <c r="G11">
-        <v>-6.932134535352932</v>
+        <v>-8.3703083496142</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-13.95590578339531</v>
       </c>
       <c r="E12">
-        <v>-17.42609988968204</v>
+        <v>-18.90522629785939</v>
       </c>
       <c r="F12">
-        <v>-4.17462974161966</v>
+        <v>-4.570384753409332</v>
       </c>
       <c r="G12">
-        <v>-6.426276555861216</v>
+        <v>-8.441912139083097</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-13.05182607572972</v>
       </c>
       <c r="E13">
-        <v>-15.80855614498623</v>
+        <v>-20.42976877185967</v>
       </c>
       <c r="F13">
-        <v>-4.187534049020471</v>
+        <v>-4.873699761618399</v>
       </c>
       <c r="G13">
-        <v>-5.53522336069314</v>
+        <v>-7.697095672021247</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-12.16919077329774</v>
       </c>
       <c r="E14">
-        <v>-17.61259150626591</v>
+        <v>-20.75418412129516</v>
       </c>
       <c r="F14">
-        <v>-3.762773752621773</v>
+        <v>-4.71497462683318</v>
       </c>
       <c r="G14">
-        <v>-6.539464107848898</v>
+        <v>-7.521593721347863</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-11.35146609147706</v>
       </c>
       <c r="E15">
-        <v>-18.66134080170229</v>
+        <v>-21.39993545784094</v>
       </c>
       <c r="F15">
-        <v>-3.412368542665763</v>
+        <v>-4.456929897187107</v>
       </c>
       <c r="G15">
-        <v>-5.388711857307155</v>
+        <v>-7.166716481720149</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-10.62951606806162</v>
       </c>
       <c r="E16">
-        <v>-18.13466568918821</v>
+        <v>-22.20239463742215</v>
       </c>
       <c r="F16">
-        <v>-3.366221851390608</v>
+        <v>-4.467400461158492</v>
       </c>
       <c r="G16">
-        <v>-5.113883608819019</v>
+        <v>-6.580369208532133</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-10.04811518438132</v>
       </c>
       <c r="E17">
-        <v>-19.72674129606488</v>
+        <v>-23.09801358428916</v>
       </c>
       <c r="F17">
-        <v>-3.249646535162037</v>
+        <v>-4.194353169480316</v>
       </c>
       <c r="G17">
-        <v>-4.681638919938536</v>
+        <v>-6.483512577689676</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-9.62052519854638</v>
       </c>
       <c r="E18">
-        <v>-20.16321826329418</v>
+        <v>-23.73850736251203</v>
       </c>
       <c r="F18">
-        <v>-3.10119564127374</v>
+        <v>-3.837852003807104</v>
       </c>
       <c r="G18">
-        <v>-5.122557238131908</v>
+        <v>-6.893146240536936</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-9.357747596771281</v>
       </c>
       <c r="E19">
-        <v>-21.03525291752924</v>
+        <v>-23.94657715774246</v>
       </c>
       <c r="F19">
-        <v>-3.047493410917651</v>
+        <v>-3.919823928518532</v>
       </c>
       <c r="G19">
-        <v>-5.736895173854463</v>
+        <v>-6.891835264503384</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-9.269769446917037</v>
       </c>
       <c r="E20">
-        <v>-20.71680609683585</v>
+        <v>-25.63300804904295</v>
       </c>
       <c r="F20">
-        <v>-2.212615868699544</v>
+        <v>-3.277760496445649</v>
       </c>
       <c r="G20">
-        <v>-4.677530532924301</v>
+        <v>-7.614034084440933</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-9.337125632312699</v>
       </c>
       <c r="E21">
-        <v>-21.48441414045403</v>
+        <v>-25.88817850242716</v>
       </c>
       <c r="F21">
-        <v>-2.058136116853673</v>
+        <v>-3.113092653912747</v>
       </c>
       <c r="G21">
-        <v>-5.07217735611528</v>
+        <v>-7.296013148301925</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-9.552292428974686</v>
       </c>
       <c r="E22">
-        <v>-23.56075117228895</v>
+        <v>-25.97883402358671</v>
       </c>
       <c r="F22">
-        <v>-1.282946587844284</v>
+        <v>-2.826144528848192</v>
       </c>
       <c r="G22">
-        <v>-5.113287710621949</v>
+        <v>-7.736315705024992</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-9.887298803351266</v>
       </c>
       <c r="E23">
-        <v>-23.09886040892859</v>
+        <v>-26.22705326936914</v>
       </c>
       <c r="F23">
-        <v>-1.221760058003901</v>
+        <v>-2.438904305591896</v>
       </c>
       <c r="G23">
-        <v>-5.227869002281665</v>
+        <v>-7.352517539566206</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-10.30340739110688</v>
       </c>
       <c r="E24">
-        <v>-23.45819482143724</v>
+        <v>-27.22108954184485</v>
       </c>
       <c r="F24">
-        <v>-1.136314788772535</v>
+        <v>-2.530548248098411</v>
       </c>
       <c r="G24">
-        <v>-6.942413779252369</v>
+        <v>-7.980925293830662</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-10.77530034365027</v>
       </c>
       <c r="E25">
-        <v>-22.97109857175019</v>
+        <v>-26.34643290115935</v>
       </c>
       <c r="F25">
-        <v>-1.434788817879642</v>
+        <v>-2.440043310770745</v>
       </c>
       <c r="G25">
-        <v>-6.575337179312441</v>
+        <v>-8.422648074590077</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-11.25539503627446</v>
       </c>
       <c r="E26">
-        <v>-23.86625561426841</v>
+        <v>-27.62906882214389</v>
       </c>
       <c r="F26">
-        <v>-1.101813286445936</v>
+        <v>-2.392433722662247</v>
       </c>
       <c r="G26">
-        <v>-5.876732617433278</v>
+        <v>-8.690825437089819</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-11.71570271840487</v>
       </c>
       <c r="E27">
-        <v>-23.62956586330951</v>
+        <v>-26.58053236498587</v>
       </c>
       <c r="F27">
-        <v>-1.374724725870053</v>
+        <v>-1.916596292206932</v>
       </c>
       <c r="G27">
-        <v>-6.577277158998454</v>
+        <v>-8.463821329461993</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-12.13263376335381</v>
       </c>
       <c r="E28">
-        <v>-23.26975143255605</v>
+        <v>-26.36910244204175</v>
       </c>
       <c r="F28">
-        <v>-0.8681217300747645</v>
+        <v>-1.828779407101351</v>
       </c>
       <c r="G28">
-        <v>-6.29938996643203</v>
+        <v>-8.807121591338875</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-12.48128669228306</v>
       </c>
       <c r="E29">
-        <v>-23.06401832991358</v>
+        <v>-26.30435884915408</v>
       </c>
       <c r="F29">
-        <v>-0.9444044274637653</v>
+        <v>-2.096074515534487</v>
       </c>
       <c r="G29">
-        <v>-6.934696897600328</v>
+        <v>-8.855131122749388</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-12.76532240869834</v>
       </c>
       <c r="E30">
-        <v>-23.1100230973575</v>
+        <v>-25.6351636026706</v>
       </c>
       <c r="F30">
-        <v>-0.8908587585468053</v>
+        <v>-1.842871593357776</v>
       </c>
       <c r="G30">
-        <v>-6.706587067762387</v>
+        <v>-9.109983539453561</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-12.98216582565563</v>
       </c>
       <c r="E31">
-        <v>-22.4355657640771</v>
+        <v>-25.63061248629289</v>
       </c>
       <c r="F31">
-        <v>-0.936580497344324</v>
+        <v>-1.901837270191254</v>
       </c>
       <c r="G31">
-        <v>-7.121590435474344</v>
+        <v>-9.161389690587365</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-13.1413441607175</v>
       </c>
       <c r="E32">
-        <v>-22.38518649074177</v>
+        <v>-25.62846598961325</v>
       </c>
       <c r="F32">
-        <v>-0.7091646524167617</v>
+        <v>-1.544776956521152</v>
       </c>
       <c r="G32">
-        <v>-6.656952058492093</v>
+        <v>-8.819883744392767</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-13.26570861472888</v>
       </c>
       <c r="E33">
-        <v>-22.14022774624485</v>
+        <v>-25.09884736899418</v>
       </c>
       <c r="F33">
-        <v>-0.9449006195380422</v>
+        <v>-1.90892892352662</v>
       </c>
       <c r="G33">
-        <v>-6.419814370968559</v>
+        <v>-8.374562400632163</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-13.36289722977499</v>
       </c>
       <c r="E34">
-        <v>-22.13555888954295</v>
+        <v>-24.67941557792975</v>
       </c>
       <c r="F34">
-        <v>-1.062913153210471</v>
+        <v>-1.731661612797137</v>
       </c>
       <c r="G34">
-        <v>-7.317028491385218</v>
+        <v>-8.569361521253958</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-13.45665700652065</v>
       </c>
       <c r="E35">
-        <v>-21.42831540444701</v>
+        <v>-24.41034270934199</v>
       </c>
       <c r="F35">
-        <v>-0.4709021647169427</v>
+        <v>-1.829486832863342</v>
       </c>
       <c r="G35">
-        <v>-7.292695981671575</v>
+        <v>-8.835516140429204</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-13.55567366328205</v>
       </c>
       <c r="E36">
-        <v>-20.12188688102617</v>
+        <v>-24.20681044506724</v>
       </c>
       <c r="F36">
-        <v>-0.5781003619458239</v>
+        <v>-1.630858411917868</v>
       </c>
       <c r="G36">
-        <v>-5.89121294362205</v>
+        <v>-8.555553235809658</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-13.65685805010723</v>
       </c>
       <c r="E37">
-        <v>-20.38856418686387</v>
+        <v>-23.67180294037905</v>
       </c>
       <c r="F37">
-        <v>-0.880650787042107</v>
+        <v>-1.749014253150981</v>
       </c>
       <c r="G37">
-        <v>-7.024379576259185</v>
+        <v>-8.199484199787808</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-13.76824630365872</v>
       </c>
       <c r="E38">
-        <v>-18.66568360827565</v>
+        <v>-23.31263608140869</v>
       </c>
       <c r="F38">
-        <v>-0.5492226459168303</v>
+        <v>-1.630306719227604</v>
       </c>
       <c r="G38">
-        <v>-6.052757634301866</v>
+        <v>-8.23263269227253</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-13.87017519348218</v>
       </c>
       <c r="E39">
-        <v>-18.3018614780254</v>
+        <v>-22.832246501727</v>
       </c>
       <c r="F39">
-        <v>-0.5981567935024056</v>
+        <v>-1.839308785158336</v>
       </c>
       <c r="G39">
-        <v>-6.648930606650439</v>
+        <v>-7.581190162145823</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-13.95694308582658</v>
       </c>
       <c r="E40">
-        <v>-17.17922107220587</v>
+        <v>-22.83296200062021</v>
       </c>
       <c r="F40">
-        <v>-0.5104840443249115</v>
+        <v>-1.535721244073748</v>
       </c>
       <c r="G40">
-        <v>-5.318726924606962</v>
+        <v>-8.14128480920742</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-14.01655305606627</v>
       </c>
       <c r="E41">
-        <v>-17.17854632957873</v>
+        <v>-21.70301263775229</v>
       </c>
       <c r="F41">
-        <v>-0.56392865241873</v>
+        <v>-1.888098796815824</v>
       </c>
       <c r="G41">
-        <v>-5.337656624000515</v>
+        <v>-7.579326325007214</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-14.03039918159991</v>
       </c>
       <c r="E42">
-        <v>-17.72196773897318</v>
+        <v>-20.97599783513887</v>
       </c>
       <c r="F42">
-        <v>-0.8235216007406363</v>
+        <v>-2.206515771145328</v>
       </c>
       <c r="G42">
-        <v>-5.737239470590548</v>
+        <v>-7.366802543568161</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-14.00402261751635</v>
       </c>
       <c r="E43">
-        <v>-17.04954821899623</v>
+        <v>-21.46193479547996</v>
       </c>
       <c r="F43">
-        <v>-0.9910506242828083</v>
+        <v>-2.17060024566215</v>
       </c>
       <c r="G43">
-        <v>-5.819950140343699</v>
+        <v>-7.211941844332133</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-13.92797391808994</v>
       </c>
       <c r="E44">
-        <v>-16.4437334947241</v>
+        <v>-20.7305907717152</v>
       </c>
       <c r="F44">
-        <v>-0.6943633836635401</v>
+        <v>-2.002295041863555</v>
       </c>
       <c r="G44">
-        <v>-5.94517483591217</v>
+        <v>-7.199120101458536</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-13.80950729450961</v>
       </c>
       <c r="E45">
-        <v>-15.12925787299163</v>
+        <v>-19.0587913799335</v>
       </c>
       <c r="F45">
-        <v>-1.227049183870776</v>
+        <v>-2.065236053863067</v>
       </c>
       <c r="G45">
-        <v>-6.078060133858516</v>
+        <v>-7.343973021529346</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-13.66199514358438</v>
       </c>
       <c r="E46">
-        <v>-15.83823123515849</v>
+        <v>-19.37007868322076</v>
       </c>
       <c r="F46">
-        <v>-1.356757436903331</v>
+        <v>-2.426829193961288</v>
       </c>
       <c r="G46">
-        <v>-5.062311930408252</v>
+        <v>-7.060825372101021</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-13.48626988135655</v>
       </c>
       <c r="E47">
-        <v>-14.75778715014243</v>
+        <v>-18.78803391901489</v>
       </c>
       <c r="F47">
-        <v>-0.9946523657501806</v>
+        <v>-2.37971993976408</v>
       </c>
       <c r="G47">
-        <v>-4.863457391500849</v>
+        <v>-6.887885783675034</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-13.30366397133803</v>
       </c>
       <c r="E48">
-        <v>-13.29768938974531</v>
+        <v>-18.14367282398947</v>
       </c>
       <c r="F48">
-        <v>-1.362317438910921</v>
+        <v>-2.334617819783855</v>
       </c>
       <c r="G48">
-        <v>-5.607436290541263</v>
+        <v>-7.04706674483981</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-13.12004431734402</v>
       </c>
       <c r="E49">
-        <v>-12.85629902821768</v>
+        <v>-17.25896749948095</v>
       </c>
       <c r="F49">
-        <v>-1.295613153800491</v>
+        <v>-2.55026670575465</v>
       </c>
       <c r="G49">
-        <v>-5.173801172534287</v>
+        <v>-6.776121766269238</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-12.93957289429949</v>
       </c>
       <c r="E50">
-        <v>-12.12757699090336</v>
+        <v>-17.43638405415345</v>
       </c>
       <c r="F50">
-        <v>-1.347859114262459</v>
+        <v>-2.516759244311411</v>
       </c>
       <c r="G50">
-        <v>-5.786093191113572</v>
+        <v>-6.455217344965525</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-12.77468253931188</v>
       </c>
       <c r="E51">
-        <v>-12.42012094027288</v>
+        <v>-16.62768916586368</v>
       </c>
       <c r="F51">
-        <v>-1.342560876354153</v>
+        <v>-2.456835146392894</v>
       </c>
       <c r="G51">
-        <v>-5.979806452798487</v>
+        <v>-7.148786567079457</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-12.61165302693846</v>
       </c>
       <c r="E52">
-        <v>-12.87587562135284</v>
+        <v>-16.01101516092115</v>
       </c>
       <c r="F52">
-        <v>-1.557256311444326</v>
+        <v>-2.606088728294504</v>
       </c>
       <c r="G52">
-        <v>-5.054426210933708</v>
+        <v>-7.161022343392603</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-12.45131910104981</v>
       </c>
       <c r="E53">
-        <v>-10.98663249314482</v>
+        <v>-15.79579490523261</v>
       </c>
       <c r="F53">
-        <v>-1.567211630891171</v>
+        <v>-2.766574143810671</v>
       </c>
       <c r="G53">
-        <v>-4.703905649235675</v>
+        <v>-7.454435994538208</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-12.28409326247737</v>
       </c>
       <c r="E54">
-        <v>-10.41030719161064</v>
+        <v>-14.46470884084001</v>
       </c>
       <c r="F54">
-        <v>-1.689912724063445</v>
+        <v>-2.975388998708371</v>
       </c>
       <c r="G54">
-        <v>-5.13222403110658</v>
+        <v>-7.260931297222268</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-12.09731020398956</v>
       </c>
       <c r="E55">
-        <v>-8.971357404829339</v>
+        <v>-14.49820143460074</v>
       </c>
       <c r="F55">
-        <v>-1.097485895133711</v>
+        <v>-2.66151810468543</v>
       </c>
       <c r="G55">
-        <v>-6.523086839066123</v>
+        <v>-7.235436786024341</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-11.89695162227487</v>
       </c>
       <c r="E56">
-        <v>-9.408092495077083</v>
+        <v>-14.59028795354672</v>
       </c>
       <c r="F56">
-        <v>-1.743094739690576</v>
+        <v>-2.37125153980526</v>
       </c>
       <c r="G56">
-        <v>-7.087114414228374</v>
+        <v>-7.298823801464766</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-11.67156227437328</v>
       </c>
       <c r="E57">
-        <v>-9.491751523894786</v>
+        <v>-14.11851605990163</v>
       </c>
       <c r="F57">
-        <v>-2.021638249086326</v>
+        <v>-2.626481477016622</v>
       </c>
       <c r="G57">
-        <v>-6.70430279134029</v>
+        <v>-7.354275439247559</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-11.42688977839679</v>
       </c>
       <c r="E58">
-        <v>-8.855845089841685</v>
+        <v>-14.26931877283106</v>
       </c>
       <c r="F58">
-        <v>-1.177999064848809</v>
+        <v>-2.528495553674274</v>
       </c>
       <c r="G58">
-        <v>-6.720173546655555</v>
+        <v>-7.387149156452521</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-11.1646611596212</v>
       </c>
       <c r="E59">
-        <v>-8.292647834455737</v>
+        <v>-13.72417201483969</v>
       </c>
       <c r="F59">
-        <v>-1.299363173032965</v>
+        <v>-2.791874969394377</v>
       </c>
       <c r="G59">
-        <v>-6.73477967357482</v>
+        <v>-7.49998910115858</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-10.87682629699188</v>
       </c>
       <c r="E60">
-        <v>-7.304475935819966</v>
+        <v>-13.59987898875116</v>
       </c>
       <c r="F60">
-        <v>-1.485699450088297</v>
+        <v>-2.654930098730965</v>
       </c>
       <c r="G60">
-        <v>-6.543148745034107</v>
+        <v>-7.536295854087767</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-10.57135281728116</v>
       </c>
       <c r="E61">
-        <v>-7.682571816142387</v>
+        <v>-13.64854197043758</v>
       </c>
       <c r="F61">
-        <v>-1.888685280937006</v>
+        <v>-2.49036497375601</v>
       </c>
       <c r="G61">
-        <v>-6.48553863155971</v>
+        <v>-7.275299064862705</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-10.24267901280484</v>
       </c>
       <c r="E62">
-        <v>-7.840117426869238</v>
+        <v>-13.08534924352564</v>
       </c>
       <c r="F62">
-        <v>-1.518232751465844</v>
+        <v>-2.685271539960706</v>
       </c>
       <c r="G62">
-        <v>-6.650135645226734</v>
+        <v>-7.831702453648013</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.891576672790755</v>
       </c>
       <c r="E63">
-        <v>-8.54574877521844</v>
+        <v>-12.26639283313449</v>
       </c>
       <c r="F63">
-        <v>-1.740890454031726</v>
+        <v>-2.695815000263538</v>
       </c>
       <c r="G63">
-        <v>-6.294871071770925</v>
+        <v>-8.062401130097665</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.524666226362672</v>
       </c>
       <c r="E64">
-        <v>-7.408091949589471</v>
+        <v>-12.35877370289097</v>
       </c>
       <c r="F64">
-        <v>-1.713358006664879</v>
+        <v>-2.51387404064746</v>
       </c>
       <c r="G64">
-        <v>-6.985755441452508</v>
+        <v>-7.825309790211681</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.13668776652236</v>
       </c>
       <c r="E65">
-        <v>-7.774748904568517</v>
+        <v>-12.51003832016918</v>
       </c>
       <c r="F65">
-        <v>-1.840654882187885</v>
+        <v>-2.578479242759196</v>
       </c>
       <c r="G65">
-        <v>-6.457564521752868</v>
+        <v>-8.299340184888843</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.738705825892261</v>
       </c>
       <c r="E66">
-        <v>-6.285759480002457</v>
+        <v>-11.28302111694685</v>
       </c>
       <c r="F66">
-        <v>-1.90079766910074</v>
+        <v>-2.812884851831581</v>
       </c>
       <c r="G66">
-        <v>-6.226269947106148</v>
+        <v>-8.086528385987874</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.333815884923542</v>
       </c>
       <c r="E67">
-        <v>-5.859145529161855</v>
+        <v>-11.8736156400792</v>
       </c>
       <c r="F67">
-        <v>-1.630150986155877</v>
+        <v>-2.641928043976624</v>
       </c>
       <c r="G67">
-        <v>-6.631930955306282</v>
+        <v>-8.237840180405803</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.926195922888752</v>
       </c>
       <c r="E68">
-        <v>-5.94962443983511</v>
+        <v>-12.00963288537359</v>
       </c>
       <c r="F68">
-        <v>-1.866570356384467</v>
+        <v>-2.64941317182832</v>
       </c>
       <c r="G68">
-        <v>-6.209432512493414</v>
+        <v>-7.76526311522038</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.530178512104115</v>
       </c>
       <c r="E69">
-        <v>-4.866250432136083</v>
+        <v>-11.49395743622414</v>
       </c>
       <c r="F69">
-        <v>-1.389294880117893</v>
+        <v>-2.656364831072614</v>
       </c>
       <c r="G69">
-        <v>-7.092646335824496</v>
+        <v>-7.803427084197098</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.1450047793636</v>
       </c>
       <c r="E70">
-        <v>-6.620096715988759</v>
+        <v>-12.29322857010395</v>
       </c>
       <c r="F70">
-        <v>-1.474209165844065</v>
+        <v>-2.726897001951381</v>
       </c>
       <c r="G70">
-        <v>-8.055091445546955</v>
+        <v>-8.257633932185104</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-6.781810453509358</v>
       </c>
       <c r="E71">
-        <v>-6.892144791999556</v>
+        <v>-11.25708654630492</v>
       </c>
       <c r="F71">
-        <v>-2.199347908008904</v>
+        <v>-2.787793603200784</v>
       </c>
       <c r="G71">
-        <v>-6.035628871681677</v>
+        <v>-8.34427753003891</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-6.443894391657117</v>
       </c>
       <c r="E72">
-        <v>-6.890795306745271</v>
+        <v>-11.897113891705</v>
       </c>
       <c r="F72">
-        <v>-1.951963438469457</v>
+        <v>-2.971276154553471</v>
       </c>
       <c r="G72">
-        <v>-6.424929163826733</v>
+        <v>-8.002182306738323</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-6.128087700828133</v>
       </c>
       <c r="E73">
-        <v>-7.13175540869341</v>
+        <v>-12.19343005992291</v>
       </c>
       <c r="F73">
-        <v>-2.246596327929783</v>
+        <v>-3.238939886480853</v>
       </c>
       <c r="G73">
-        <v>-7.236943084244709</v>
+        <v>-8.439008790645156</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.839708421027666</v>
       </c>
       <c r="E74">
-        <v>-6.817832533533686</v>
+        <v>-12.42259348708106</v>
       </c>
       <c r="F74">
-        <v>-2.144104085916205</v>
+        <v>-3.177623302958231</v>
       </c>
       <c r="G74">
-        <v>-6.915009083278282</v>
+        <v>-7.946392993310525</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.572210442614375</v>
       </c>
       <c r="E75">
-        <v>-7.403744614542108</v>
+        <v>-12.67723863748038</v>
       </c>
       <c r="F75">
-        <v>-2.185580441774376</v>
+        <v>-3.238159564387416</v>
       </c>
       <c r="G75">
-        <v>-5.939977279415515</v>
+        <v>-7.360254284491482</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.325109355597196</v>
       </c>
       <c r="E76">
-        <v>-7.338466661721539</v>
+        <v>-13.51579881185074</v>
       </c>
       <c r="F76">
-        <v>-2.18509336174153</v>
+        <v>-3.190506901173972</v>
       </c>
       <c r="G76">
-        <v>-5.587318105299112</v>
+        <v>-7.76099251147472</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.098595798835748</v>
       </c>
       <c r="E77">
-        <v>-6.808594446558038</v>
+        <v>-13.23810825722639</v>
       </c>
       <c r="F77">
-        <v>-2.464942378164093</v>
+        <v>-3.405644684457239</v>
       </c>
       <c r="G77">
-        <v>-6.615063725783696</v>
+        <v>-7.877255560268385</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.88536847809603</v>
       </c>
       <c r="E78">
-        <v>-9.647617070764792</v>
+        <v>-13.04108341010067</v>
       </c>
       <c r="F78">
-        <v>-2.837987697606017</v>
+        <v>-3.536438927154865</v>
       </c>
       <c r="G78">
-        <v>-5.215325345233366</v>
+        <v>-7.382312449419646</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.687693968747282</v>
       </c>
       <c r="E79">
-        <v>-9.409546135233546</v>
+        <v>-13.93610459839866</v>
       </c>
       <c r="F79">
-        <v>-2.986013639016677</v>
+        <v>-3.647663818328754</v>
       </c>
       <c r="G79">
-        <v>-6.112479875830318</v>
+        <v>-7.653538824361056</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.501279507881891</v>
       </c>
       <c r="E80">
-        <v>-8.801367547529409</v>
+        <v>-14.12323020134361</v>
       </c>
       <c r="F80">
-        <v>-3.520561609145407</v>
+        <v>-3.692611861972058</v>
       </c>
       <c r="G80">
-        <v>-5.831378143545263</v>
+        <v>-7.121530845654637</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.323042310861983</v>
       </c>
       <c r="E81">
-        <v>-10.50836676777273</v>
+        <v>-14.62199632854843</v>
       </c>
       <c r="F81">
-        <v>-2.756728168860997</v>
+        <v>-3.904302808492278</v>
       </c>
       <c r="G81">
-        <v>-5.198425010255387</v>
+        <v>-7.001867866592141</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.155585781721287</v>
       </c>
       <c r="E82">
-        <v>-10.24548432315346</v>
+        <v>-16.3419515129277</v>
       </c>
       <c r="F82">
-        <v>-3.073495863691527</v>
+        <v>-3.815955768248905</v>
       </c>
       <c r="G82">
-        <v>-5.1483099718819</v>
+        <v>-7.40645956858309</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.993660514551909</v>
       </c>
       <c r="E83">
-        <v>-12.25663850012197</v>
+        <v>-16.91858927916841</v>
       </c>
       <c r="F83">
-        <v>-3.52999588549589</v>
+        <v>-3.858020264963064</v>
       </c>
       <c r="G83">
-        <v>-5.460848644607874</v>
+        <v>-7.034973321984853</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.841308512822209</v>
       </c>
       <c r="E84">
-        <v>-11.93038006176535</v>
+        <v>-17.26372692566301</v>
       </c>
       <c r="F84">
-        <v>-3.457873249203749</v>
+        <v>-4.081253682873891</v>
       </c>
       <c r="G84">
-        <v>-4.622317254420336</v>
+        <v>-6.973470006956273</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.700877320535705</v>
       </c>
       <c r="E85">
-        <v>-14.06892474104363</v>
+        <v>-18.16514684773384</v>
       </c>
       <c r="F85">
-        <v>-3.62976942569348</v>
+        <v>-4.264870429745832</v>
       </c>
       <c r="G85">
-        <v>-4.855091642923111</v>
+        <v>-7.169427818516812</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.572643155480327</v>
       </c>
       <c r="E86">
-        <v>-15.76002448904603</v>
+        <v>-19.17707964948785</v>
       </c>
       <c r="F86">
-        <v>-3.71334589806413</v>
+        <v>-4.489117769357686</v>
       </c>
       <c r="G86">
-        <v>-4.680963568648525</v>
+        <v>-5.90493184433679</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.465215680742309</v>
       </c>
       <c r="E87">
-        <v>-16.93881797256067</v>
+        <v>-20.52880649840742</v>
       </c>
       <c r="F87">
-        <v>-3.994106946997175</v>
+        <v>-4.393287257997423</v>
       </c>
       <c r="G87">
-        <v>-4.27830522525251</v>
+        <v>-6.840276828274774</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.382262169622143</v>
       </c>
       <c r="E88">
-        <v>-17.67667394194846</v>
+        <v>-21.57974757526351</v>
       </c>
       <c r="F88">
-        <v>-4.457898258680979</v>
+        <v>-4.410482508544735</v>
       </c>
       <c r="G88">
-        <v>-4.867446598875671</v>
+        <v>-6.614865093051339</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.33305573157561</v>
       </c>
       <c r="E89">
-        <v>-18.29020065745565</v>
+        <v>-23.09618408079006</v>
       </c>
       <c r="F89">
-        <v>-3.903928386426212</v>
+        <v>-4.657537287857868</v>
       </c>
       <c r="G89">
-        <v>-3.728181941355199</v>
+        <v>-6.32628483839307</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.330600197023495</v>
       </c>
       <c r="E90">
-        <v>-20.98068480573681</v>
+        <v>-24.03307101128896</v>
       </c>
       <c r="F90">
-        <v>-4.080730983042725</v>
+        <v>-4.695111204881451</v>
       </c>
       <c r="G90">
-        <v>-5.298817303733785</v>
+        <v>-6.868919668280549</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.381655680834905</v>
       </c>
       <c r="E91">
-        <v>-23.30518221319206</v>
+        <v>-26.42882395725491</v>
       </c>
       <c r="F91">
-        <v>-4.329956084951192</v>
+        <v>-4.872808438292987</v>
       </c>
       <c r="G91">
-        <v>-4.553865104304826</v>
+        <v>-6.509589744902515</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.499803849385477</v>
       </c>
       <c r="E92">
-        <v>-24.29626139214076</v>
+        <v>-27.69017152192938</v>
       </c>
       <c r="F92">
-        <v>-4.816689031855529</v>
+        <v>-5.171547544968989</v>
       </c>
       <c r="G92">
-        <v>-4.967050982515723</v>
+        <v>-6.936107190000058</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.691303837129096</v>
       </c>
       <c r="E93">
-        <v>-26.10749702709264</v>
+        <v>-28.55104801620954</v>
       </c>
       <c r="F93">
-        <v>-4.906686179965278</v>
+        <v>-5.148356571160214</v>
       </c>
       <c r="G93">
-        <v>-5.779717080404936</v>
+        <v>-7.197385375595958</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-3.954633213695898</v>
       </c>
       <c r="E94">
-        <v>-28.9899160177149</v>
+        <v>-32.19022029825359</v>
       </c>
       <c r="F94">
-        <v>-4.332444500629202</v>
+        <v>-5.411340027261779</v>
       </c>
       <c r="G94">
-        <v>-5.781673612818645</v>
+        <v>-7.551084061011691</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.288062862052159</v>
       </c>
       <c r="E95">
-        <v>-29.58078677776172</v>
+        <v>-33.51568652640267</v>
       </c>
       <c r="F95">
-        <v>-4.656875422303031</v>
+        <v>-5.759605564216359</v>
       </c>
       <c r="G95">
-        <v>-5.735855662555132</v>
+        <v>-7.648821296967594</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.676459588168827</v>
       </c>
       <c r="E96">
-        <v>-31.92835676028605</v>
+        <v>-35.05984182133017</v>
       </c>
       <c r="F96">
-        <v>-5.217783699923647</v>
+        <v>-5.590624412617078</v>
       </c>
       <c r="G96">
-        <v>-5.110275114181213</v>
+        <v>-8.318643975928333</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.098751579470553</v>
       </c>
       <c r="E97">
-        <v>-35.05503258193403</v>
+        <v>-37.45947566952069</v>
       </c>
       <c r="F97">
-        <v>-5.211054871510706</v>
+        <v>-5.882601556184029</v>
       </c>
       <c r="G97">
-        <v>-6.780547965655244</v>
+        <v>-8.498443014711691</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.539675596284128</v>
       </c>
       <c r="E98">
-        <v>-37.68923685524786</v>
+        <v>-40.00163644439162</v>
       </c>
       <c r="F98">
-        <v>-5.222478057995311</v>
+        <v>-5.956849783231754</v>
       </c>
       <c r="G98">
-        <v>-7.664503351187122</v>
+        <v>-8.536120333494138</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.959476814513345</v>
       </c>
       <c r="E99">
-        <v>-39.3222634525759</v>
+        <v>-42.35916680549582</v>
       </c>
       <c r="F99">
-        <v>-5.653332653376404</v>
+        <v>-5.749238546170322</v>
       </c>
       <c r="G99">
-        <v>-7.341903930567302</v>
+        <v>-9.383633233729718</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-6.356764772095997</v>
       </c>
       <c r="E100">
-        <v>-42.14532547014262</v>
+        <v>-45.42233530766023</v>
       </c>
       <c r="F100">
-        <v>-6.036305127773478</v>
+        <v>-6.102133828539149</v>
       </c>
       <c r="G100">
-        <v>-7.737073819953486</v>
+        <v>-9.257057835581223</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-6.680957277366772</v>
       </c>
       <c r="E101">
-        <v>-44.75189246658763</v>
+        <v>-47.20140519173563</v>
       </c>
       <c r="F101">
-        <v>-5.980739070761089</v>
+        <v>-6.08720913304291</v>
       </c>
       <c r="G101">
-        <v>-8.319551065406094</v>
+        <v>-9.509314784582608</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-6.967152667051817</v>
       </c>
       <c r="E102">
-        <v>-48.20484936896227</v>
+        <v>-49.37023630517722</v>
       </c>
       <c r="F102">
-        <v>-5.763039147100963</v>
+        <v>-6.239695004550242</v>
       </c>
       <c r="G102">
-        <v>-9.112320784604286</v>
+        <v>-10.8028243798688</v>
       </c>
     </row>
   </sheetData>
